--- a/artfynd/A 32950-2025 artfynd.xlsx
+++ b/artfynd/A 32950-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,6 +1264,233 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120975276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97042</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Valås, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>345126</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6430476</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120975202</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97042</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Valås, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>345227</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6430555</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
